--- a/docs/financial/tco-roi-model.xlsx
+++ b/docs/financial/tco-roi-model.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +129,7 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -792,11 +793,11 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>LLM cost per incident (as built)</t>
+          <t>LLM cost per incident (as built, measured on OpenAI)</t>
         </is>
       </c>
       <c r="B17" s="14">
-        <f>'Token Economics'!F20</f>
+        <f>'Token Economics'!B45</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1814,6 +1815,246 @@
       <c r="E27" s="6">
         <f>SUM(B27:D27)</f>
         <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Measured on OpenAI (token ledger, live rehearsals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Avg LLM cost, P1 / tier-1 incident (gpt-5.4 triage + planner, mini summary)</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>n = 21 incidents</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Avg LLM cost, P2 incident (all gpt-5.4-mini)</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>n = 7 incidents</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Avg LLM cost, semantic-cache hit (summary call only)</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>n = 13 incidents</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Share of input tokens served from the prompt cache</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OpenAI automatic prompt caching</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Avg triage call on gpt-5.4</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>0.00576</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>measured per call</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Avg planner call on gpt-5.4</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>measured per call</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Avg summary call: input tokens</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>3138</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>measured on gpt-5.4-mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Avg summary call: output tokens</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>measured on gpt-5.4-mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>gpt-5.4 price $/1M: input / cached input / output</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Summary call on gpt-5.4 (estimate from measured tokens)</t>
+        </is>
+      </c>
+      <c r="B40" s="22">
+        <f>(B37*((1-B34)*B39+B34*C39)+B38*D39)/1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI strategy (measured)</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>$ per incident</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>vs all-deep</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>All gpt-5.4 (no routing, no semantic cache)</t>
+        </is>
+      </c>
+      <c r="B43" s="22">
+        <f>B35+B36+B40</f>
+        <v/>
+      </c>
+      <c r="C43" s="19">
+        <f>1-B43/$B$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Tiered routing (gpt-5.4 for P1/tier-1, mini otherwise)</t>
+        </is>
+      </c>
+      <c r="B44" s="22">
+        <f>$B$13*B31+(1-$B$13)*B32</f>
+        <v/>
+      </c>
+      <c r="C44" s="19">
+        <f>1-B44/$B$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Tiered routing + semantic cache (as built)</t>
+        </is>
+      </c>
+      <c r="B45" s="24">
+        <f>(1-$B$14)*B44+$B$14*B33</f>
+        <v/>
+      </c>
+      <c r="C45" s="19">
+        <f>1-B45/$B$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Measured costs already include retries and re-plans that happened, so no overhead multiplier is applied. The Claude rows above are modeled.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1872,15 +2113,15 @@
           <t>Incidents per month</t>
         </is>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>Inputs!B5</f>
         <v/>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <f>B4*(1+Inputs!$B$6)</f>
         <v/>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>C4*(1+Inputs!$B$6)</f>
         <v/>
       </c>
@@ -1907,19 +2148,19 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>LLM production (all incidents x cost per incident)</t>
+          <t>LLM production (all incidents x measured cost per incident)</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>B4*'Token Economics'!$F$20</f>
+        <f>B4*'Token Economics'!$B$45</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>C4*'Token Economics'!$F$20</f>
+        <f>C4*'Token Economics'!$B$45</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>D4*'Token Economics'!$F$20</f>
+        <f>D4*'Token Economics'!$B$45</f>
         <v/>
       </c>
     </row>
@@ -2116,15 +2357,15 @@
           <t>Incidents through the platform</t>
         </is>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>TCO!B4*Inputs!B7</f>
         <v/>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>TCO!C4*Inputs!C7</f>
         <v/>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>TCO!D4*Inputs!D7</f>
         <v/>
       </c>
@@ -2135,15 +2376,15 @@
           <t>Automated incidents</t>
         </is>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>B4*Inputs!B8</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>C4*Inputs!C8</f>
         <v/>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>D4*Inputs!D8</f>
         <v/>
       </c>
@@ -2154,15 +2395,15 @@
           <t>HITL incidents</t>
         </is>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>B4*Inputs!B9</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>C4*Inputs!C9</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>D4*Inputs!D9</f>
         <v/>
       </c>
@@ -2173,15 +2414,15 @@
           <t>Escalated incidents</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>B4*Inputs!B10</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C4*Inputs!C10</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>D4*Inputs!D10</f>
         <v/>
       </c>
@@ -2192,15 +2433,15 @@
           <t>Minutes saved: automated</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>B5*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>C5*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>D5*Inputs!$B$11</f>
         <v/>
       </c>
@@ -2211,15 +2452,15 @@
           <t>Minutes saved: HITL</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>B6*Inputs!$B$12</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>C6*Inputs!$B$12</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>D6*Inputs!$B$12</f>
         <v/>
       </c>
@@ -2230,15 +2471,15 @@
           <t>Minutes saved: escalated</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>B7*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>C7*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>D7*Inputs!$B$13</f>
         <v/>
       </c>
@@ -2249,15 +2490,15 @@
           <t>Bad-remediation cleanup (minutes)</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>-(B5+B6)*Inputs!B14*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>-(C5+C6)*Inputs!C14*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>-(D5+D6)*Inputs!D14*Inputs!$B$15</f>
         <v/>
       </c>
@@ -2268,15 +2509,15 @@
           <t>Net minutes saved</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUM(B8:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>SUM(C8:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>SUM(D8:D11)</f>
         <v/>
       </c>
@@ -2287,15 +2528,15 @@
           <t>SRE hours freed</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>B12/60</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>C12/60</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>D12/60</f>
         <v/>
       </c>
